--- a/Daily_Purchase_details_List_September_2026.xlsx
+++ b/Daily_Purchase_details_List_September_2026.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A4650E-9BB3-4A47-885A-D249EB01859C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6FF2AB-A309-4964-9EFD-DBDF63304AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Date_05-09-26 to 11-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Date_12-09-26 to 18-09-2026" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Date_12-09-26 to 18-09-2026'!$A$3:$G$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="44">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -91,13 +95,88 @@
   </si>
   <si>
     <t xml:space="preserve">  TOTAL</t>
+  </si>
+  <si>
+    <t>Received money from Rajashekar hand cash</t>
+  </si>
+  <si>
+    <t>14-09-2026</t>
+  </si>
+  <si>
+    <t>All mixed fruits 4 kgs for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Coconuts 5 No's for vinayaka Puja</t>
+  </si>
+  <si>
+    <t>All mixed  flowers for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Puja samanulu for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Lemon for vinayaka puja</t>
+  </si>
+  <si>
+    <t>suger can 2 no's for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Laddu 1 Kg for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Decaration kit  for vinayaka puja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marmaralu &amp; floor wiper for office wash room cleening </t>
+  </si>
+  <si>
+    <t>Betel Leaves &amp; vokkalu for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Vinayaka Vigraham</t>
+  </si>
+  <si>
+    <t>Banana for vinayaka puja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusher pujari Amount </t>
+  </si>
+  <si>
+    <t>17-09-2026</t>
+  </si>
+  <si>
+    <t>Viswakarma Patam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puja samanulu for viswakarma puja </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweets one Kg  for viswakarma puja </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coconut 1 No's  for viswakarma puja </t>
+  </si>
+  <si>
+    <t>Murali Technical Works ,Printing papers one box &amp; Catrage 2 No's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fruits for  for viswakarma puja </t>
+  </si>
+  <si>
+    <t>pula mala for for vinayaka puja</t>
+  </si>
+  <si>
+    <t>Gst_15</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +219,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -173,7 +265,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -364,11 +456,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -433,6 +536,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -442,7 +546,60 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -770,22 +927,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -813,13 +970,13 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28">
         <v>6050</v>
       </c>
     </row>
@@ -865,7 +1022,7 @@
         <v>2000</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="G6:G12" si="0">G5-E6+F6</f>
+        <f t="shared" ref="G6:G11" si="0">G5-E6+F6</f>
         <v>5740</v>
       </c>
     </row>
@@ -1104,4 +1261,668 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F00D83-B64F-4059-BE84-CBA4EC15AA8A}">
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="56.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="42">
+        <v>179</v>
+      </c>
+      <c r="B5" s="43">
+        <v>46365</v>
+      </c>
+      <c r="C5" s="42"/>
+      <c r="D5" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42">
+        <v>14000</v>
+      </c>
+      <c r="G5" s="42">
+        <f>G4-E5+F5</f>
+        <v>14560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="42">
+        <v>180</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="42"/>
+      <c r="D6" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="42">
+        <v>750</v>
+      </c>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42">
+        <f t="shared" ref="G6:G25" si="0">G5-E6+F6</f>
+        <v>13810</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="42">
+        <v>181</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="42"/>
+      <c r="D7" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="42">
+        <v>150</v>
+      </c>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42">
+        <f t="shared" si="0"/>
+        <v>13660</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>182</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="42">
+        <v>460</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42">
+        <f t="shared" si="0"/>
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="42">
+        <v>183</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="42">
+        <v>140</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42">
+        <f t="shared" si="0"/>
+        <v>13060</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>184</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="42">
+        <v>50</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42">
+        <f t="shared" si="0"/>
+        <v>13010</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>185</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="42">
+        <v>80</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42">
+        <f t="shared" si="0"/>
+        <v>12930</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="42">
+        <v>186</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="42">
+        <v>260</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42">
+        <f t="shared" si="0"/>
+        <v>12670</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="42">
+        <v>187</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="42">
+        <v>78</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="42">
+        <v>1180</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42">
+        <f t="shared" si="0"/>
+        <v>11490</v>
+      </c>
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>188</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="42">
+        <v>199</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="42">
+        <v>500</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42">
+        <f t="shared" si="0"/>
+        <v>10990</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="42">
+        <v>189</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="42">
+        <v>50</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42">
+        <f t="shared" si="0"/>
+        <v>10940</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="42">
+        <v>190</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="42">
+        <v>900</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42">
+        <f t="shared" si="0"/>
+        <v>10040</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="42">
+        <v>191</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="D17" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="42">
+        <v>200</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42">
+        <f t="shared" si="0"/>
+        <v>9840</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="42">
+        <v>192</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="44"/>
+      <c r="D18" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="45">
+        <v>250</v>
+      </c>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42">
+        <f t="shared" si="0"/>
+        <v>9590</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="42">
+        <v>193</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="42"/>
+      <c r="D19" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="42">
+        <v>60</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42">
+        <f t="shared" si="0"/>
+        <v>9530</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="42">
+        <v>194</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="42">
+        <v>110</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42">
+        <f t="shared" si="0"/>
+        <v>9420</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="42">
+        <v>195</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="42"/>
+      <c r="D21" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="42">
+        <v>350</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42">
+        <f t="shared" si="0"/>
+        <v>9070</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="42">
+        <v>196</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="42">
+        <v>40</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42">
+        <f t="shared" si="0"/>
+        <v>9030</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="42">
+        <v>197</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="42">
+        <v>150</v>
+      </c>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42">
+        <f t="shared" si="0"/>
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42">
+        <f t="shared" si="0"/>
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="47">
+        <f>SUM(E5:E24)</f>
+        <v>5680</v>
+      </c>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47">
+        <f>G24-E24+F24</f>
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="42"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="32">
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="42">
+        <v>198</v>
+      </c>
+      <c r="B33" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="32">
+        <v>600</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42">
+        <f>G32-E33+F33</f>
+        <v>8280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="34">
+        <v>199</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="35">
+        <v>3380</v>
+      </c>
+      <c r="F34" s="35"/>
+      <c r="G34" s="42">
+        <f t="shared" ref="G34:G36" si="1">G33-E34+F34</f>
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="42">
+        <f t="shared" si="1"/>
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="34"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="42">
+        <f t="shared" si="1"/>
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="49">
+        <f>SUM(E33:E36)</f>
+        <v>3980</v>
+      </c>
+      <c r="F37" s="49"/>
+      <c r="G37" s="48">
+        <f>G36-E36+F36</f>
+        <v>4900</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{B1F00D83-B64F-4059-BE84-CBA4EC15AA8A}"/>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Daily_Purchase_details_List_September_2026.xlsx
+++ b/Daily_Purchase_details_List_September_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6FF2AB-A309-4964-9EFD-DBDF63304AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98019A09-5FFF-4E81-9CFD-DB57528BD895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>Gst_15</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -537,6 +534,60 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -545,60 +596,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -927,22 +924,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="49"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -1265,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F00D83-B64F-4059-BE84-CBA4EC15AA8A}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -1277,29 +1274,29 @@
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="49"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1322,481 +1319,478 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38">
         <v>560</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="42">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="39">
         <v>179</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="40">
         <v>46365</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="38" t="s">
+      <c r="C5" s="39"/>
+      <c r="D5" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42">
+      <c r="E5" s="39"/>
+      <c r="F5" s="39">
         <v>14000</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="39">
         <f>G4-E5+F5</f>
         <v>14560</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="42">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="39">
         <v>180</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="39"/>
+      <c r="D6" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="39">
         <v>750</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42">
-        <f t="shared" ref="G6:G25" si="0">G5-E6+F6</f>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39">
+        <f t="shared" ref="G6:G24" si="0">G5-E6+F6</f>
         <v>13810</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="42">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="39">
         <v>181</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="36" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="39">
         <v>150</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42">
+      <c r="F7" s="39"/>
+      <c r="G7" s="39">
         <f t="shared" si="0"/>
         <v>13660</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="42">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="39">
         <v>182</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="38" t="s">
+      <c r="C8" s="39"/>
+      <c r="D8" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="39">
         <v>460</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42">
+      <c r="F8" s="39"/>
+      <c r="G8" s="39">
         <f t="shared" si="0"/>
         <v>13200</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="42">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="39">
         <v>183</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="38" t="s">
+      <c r="C9" s="39"/>
+      <c r="D9" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="39">
         <v>140</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42">
+      <c r="F9" s="39"/>
+      <c r="G9" s="39">
         <f t="shared" si="0"/>
         <v>13060</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="42">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="39">
         <v>184</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="38" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="39">
         <v>50</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42">
+      <c r="F10" s="39"/>
+      <c r="G10" s="39">
         <f t="shared" si="0"/>
         <v>13010</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="42">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="39">
         <v>185</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="38" t="s">
+      <c r="C11" s="39"/>
+      <c r="D11" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="39">
         <v>80</v>
       </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42">
+      <c r="F11" s="39"/>
+      <c r="G11" s="39">
         <f t="shared" si="0"/>
         <v>12930</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="42">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="39">
         <v>186</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="39"/>
+      <c r="D12" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="39">
         <v>260</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42">
+      <c r="F12" s="39"/>
+      <c r="G12" s="39">
         <f t="shared" si="0"/>
         <v>12670</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="42">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="39">
         <v>187</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="39">
         <v>78</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="39">
         <v>1180</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42">
+      <c r="F13" s="39"/>
+      <c r="G13" s="39">
         <f t="shared" si="0"/>
         <v>11490</v>
       </c>
-      <c r="I13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="42">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="39">
         <v>188</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="39">
         <v>199</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="39">
         <v>500</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42">
+      <c r="F14" s="39"/>
+      <c r="G14" s="39">
         <f t="shared" si="0"/>
         <v>10990</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="39">
         <v>189</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="39">
         <v>50</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42">
+      <c r="F15" s="39"/>
+      <c r="G15" s="39">
         <f t="shared" si="0"/>
         <v>10940</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="42">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="39">
         <v>190</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="39"/>
+      <c r="D16" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="39">
         <v>900</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42">
+      <c r="F16" s="39"/>
+      <c r="G16" s="39">
         <f t="shared" si="0"/>
         <v>10040</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="42">
+      <c r="A17" s="39">
         <v>191</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="39"/>
+      <c r="D17" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="39">
         <v>200</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42">
+      <c r="F17" s="39"/>
+      <c r="G17" s="39">
         <f t="shared" si="0"/>
         <v>9840</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="42">
+      <c r="A18" s="39">
         <v>192</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="39" t="s">
+      <c r="C18" s="41"/>
+      <c r="D18" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="42">
         <v>250</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42">
+      <c r="F18" s="39"/>
+      <c r="G18" s="39">
         <f t="shared" si="0"/>
         <v>9590</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="42">
+      <c r="A19" s="39">
         <v>193</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="38" t="s">
+      <c r="C19" s="39"/>
+      <c r="D19" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="39">
         <v>60</v>
       </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42">
+      <c r="F19" s="39"/>
+      <c r="G19" s="39">
         <f t="shared" si="0"/>
         <v>9530</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="42">
+      <c r="A20" s="39">
         <v>194</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="39"/>
+      <c r="D20" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="39">
         <v>110</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42">
+      <c r="F20" s="39"/>
+      <c r="G20" s="39">
         <f t="shared" si="0"/>
         <v>9420</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="42">
+      <c r="A21" s="39">
         <v>195</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="38" t="s">
+      <c r="C21" s="39"/>
+      <c r="D21" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="39">
         <v>350</v>
       </c>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42">
+      <c r="F21" s="39"/>
+      <c r="G21" s="39">
         <f t="shared" si="0"/>
         <v>9070</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="42">
+      <c r="A22" s="39">
         <v>196</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="38" t="s">
+      <c r="C22" s="39"/>
+      <c r="D22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="39">
         <v>40</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42">
+      <c r="F22" s="39"/>
+      <c r="G22" s="39">
         <f t="shared" si="0"/>
         <v>9030</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="42">
+      <c r="A23" s="39">
         <v>197</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="38" t="s">
+      <c r="C23" s="39"/>
+      <c r="D23" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="39">
         <v>150</v>
       </c>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42">
+      <c r="F23" s="39"/>
+      <c r="G23" s="39">
         <f t="shared" si="0"/>
         <v>8880</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42">
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39">
         <f t="shared" si="0"/>
         <v>8880</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="47" t="s">
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="44">
         <f>SUM(E5:E24)</f>
         <v>5680</v>
       </c>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47">
+      <c r="F25" s="44"/>
+      <c r="G25" s="44">
         <f>G24-E24+F24</f>
         <v>8880</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="33" t="s">
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="33" t="s">
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1823,94 +1817,94 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
       <c r="F32" s="15"/>
-      <c r="G32" s="32">
+      <c r="G32" s="29">
         <v>8880</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="42">
+      <c r="A33" s="39">
         <v>198</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="43" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="15"/>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="29">
         <v>600</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42">
+      <c r="F33" s="39"/>
+      <c r="G33" s="39">
         <f>G32-E33+F33</f>
         <v>8280</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="34">
+      <c r="A34" s="31">
         <v>199</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="32">
         <v>3380</v>
       </c>
-      <c r="F34" s="35"/>
-      <c r="G34" s="42">
+      <c r="F34" s="32"/>
+      <c r="G34" s="39">
         <f t="shared" ref="G34:G36" si="1">G33-E34+F34</f>
         <v>4900</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="42">
+      <c r="A35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="39">
         <f t="shared" si="1"/>
         <v>4900</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="42">
+      <c r="A36" s="31"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="39">
         <f t="shared" si="1"/>
         <v>4900</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37" t="s">
+      <c r="A37" s="31"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="49">
+      <c r="E37" s="46">
         <f>SUM(E33:E36)</f>
         <v>3980</v>
       </c>
-      <c r="F37" s="49"/>
-      <c r="G37" s="48">
+      <c r="F37" s="46"/>
+      <c r="G37" s="45">
         <f>G36-E36+F36</f>
         <v>4900</v>
       </c>

--- a/Daily_Purchase_details_List_September_2026.xlsx
+++ b/Daily_Purchase_details_List_September_2026.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98019A09-5FFF-4E81-9CFD-DB57528BD895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6B1D2-A187-47E0-90C2-5BB3CFACBFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Date_05-09-26 to 11-09-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Date_12-09-26 to 18-09-2026" sheetId="2" r:id="rId2"/>
+    <sheet name="Date_19-09-26 to 25-09-2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Date_12-09-26 to 18-09-2026'!$A$3:$G$3</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -167,6 +168,30 @@
   </si>
   <si>
     <t>Gst_15</t>
+  </si>
+  <si>
+    <t>16-09-2026</t>
+  </si>
+  <si>
+    <t>Paid to lineman for crusher Electrical Purpose</t>
+  </si>
+  <si>
+    <t>17-09-2027</t>
+  </si>
+  <si>
+    <t>Paid to postman for crusher Electrical bill delivered</t>
+  </si>
+  <si>
+    <t>19-09-2026</t>
+  </si>
+  <si>
+    <t>Gireesh sir food expensive</t>
+  </si>
+  <si>
+    <t>24-09-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carpenter charges for office Door repaire                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
   </si>
 </sst>
 </file>
@@ -468,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -587,6 +612,16 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -924,22 +959,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="48"/>
-      <c r="E1" s="49"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -1277,22 +1312,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="48"/>
-      <c r="E1" s="49"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -1919,4 +1954,329 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B13B25-A20B-4D4C-9830-1B03E23D3D53}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="49.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>200</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>350</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39">
+        <f>G4-E5+F5</f>
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="47">
+        <v>201</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39">
+        <f>G5-E6+F6</f>
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39">
+        <f>G6-E7+F7</f>
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="39"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39">
+        <f>G7-E8+F8</f>
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="39"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="44">
+        <f>SUM(E5:E8)</f>
+        <v>550</v>
+      </c>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44">
+        <f>G8-E8+F8</f>
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="48"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="50">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>202</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="39">
+        <v>200</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39">
+        <f>G16-E17+F17</f>
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>203</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="39">
+        <v>50</v>
+      </c>
+      <c r="F18" s="32"/>
+      <c r="G18" s="39">
+        <f t="shared" ref="G18:G20" si="0">G17-E18+F18</f>
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="39">
+        <f t="shared" si="0"/>
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="39">
+        <f t="shared" si="0"/>
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="46">
+        <f>SUM(E17:E20)</f>
+        <v>250</v>
+      </c>
+      <c r="F21" s="46"/>
+      <c r="G21" s="45">
+        <f>G20-E20+F20</f>
+        <v>4100</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Daily_Purchase_details_List_September_2026.xlsx
+++ b/Daily_Purchase_details_List_September_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6B1D2-A187-47E0-90C2-5BB3CFACBFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0FAC33-69DA-4B6F-B695-3375DBC966A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
   </bookViews>
@@ -18,7 +18,9 @@
     <sheet name="Date_19-09-26 to 25-09-2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Date_05-09-26 to 11-09-2026'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Date_12-09-26 to 18-09-2026'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Date_19-09-26 to 25-09-2026'!$A$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -953,7 +955,7 @@
     <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1287,6 +1289,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{C53E7057-A0F4-4F3C-BDFD-8B7E6D6D0C03}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C2:E2"/>
@@ -1304,9 +1307,9 @@
     <col min="2" max="2" width="18.140625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="56.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1962,12 +1965,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="49.5703125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2272,6 +2274,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{80B13B25-A20B-4D4C-9830-1B03E23D3D53}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C2:E2"/>

--- a/Daily_Purchase_details_List_September_2026.xlsx
+++ b/Daily_Purchase_details_List_September_2026.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0FAC33-69DA-4B6F-B695-3375DBC966A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D1C88E-7522-42ED-B0DF-871B49DDD052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="3" xr2:uid="{171A3A41-9717-443B-8D79-939A542922DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Date_05-09-26 to 11-09-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Date_12-09-26 to 18-09-2026" sheetId="2" r:id="rId2"/>
     <sheet name="Date_19-09-26 to 25-09-2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Date_26-09-26 to 02-10-2026" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Date_05-09-26 to 11-09-2026'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Date_12-09-26 to 18-09-2026'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Date_19-09-26 to 25-09-2026'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Date_26-09-26 to 02-10-2026'!$A$3:$G$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="82">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -194,12 +196,154 @@
   </si>
   <si>
     <t xml:space="preserve">Carpenter charges for office Door repaire                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Received money through PhonePe from Rajasekhar</t>
+  </si>
+  <si>
+    <t>26-09-2026</t>
+  </si>
+  <si>
+    <t>Water taps for camp office washrooms</t>
+  </si>
+  <si>
+    <t>AE2627/1128</t>
+  </si>
+  <si>
+    <r>
+      <t>Paid to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Amit Engineer's   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7018 welding rods – one box of 6013 (3.15 mm), one box of 6013 (4 mm), and one box (7"&amp;4" grinding wheel &amp; 7"Cutting wheels)</t>
+    </r>
+  </si>
+  <si>
+    <t>Received money from Rajasekhar through PhonePe</t>
+  </si>
+  <si>
+    <t>27-09-2026</t>
+  </si>
+  <si>
+    <t>Delivery charges from Vizag to Sompeta for  welding rods</t>
+  </si>
+  <si>
+    <t>28-09-2026</t>
+  </si>
+  <si>
+    <t>Ananth expenses – went for Rajapuram, LC-335 electrical work</t>
+  </si>
+  <si>
+    <t>Paid to have the lease agreement written for Mirai Buildtech  Pvt  Ltd.</t>
+  </si>
+  <si>
+    <t>29-09-2026</t>
+  </si>
+  <si>
+    <t>E-stamp for land agreement – Mirai Buildtech  Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Paid to have the lease agreement written for   Mirai Buildtech  Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Tissue papers for office purpose</t>
+  </si>
+  <si>
+    <t>Hand wash – 2 Nos. for office purpose</t>
+  </si>
+  <si>
+    <t>Tape box – one box, 30 pieces for store</t>
+  </si>
+  <si>
+    <t>30-09-2026</t>
+  </si>
+  <si>
+    <t>New cartridges – 2 Nos. for office printers</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Paid  to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Amit Engineer's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for gas cutting torch, hose pipe (red/blue), safety valves and LPG regulator for workshop</t>
+    </r>
+  </si>
+  <si>
+    <t>E-Stamp for land – Mirai Buildtech  Pvt  Ltd.</t>
+  </si>
+  <si>
+    <t>L-11</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>The SAI engineer took cash for their Hyderabad expenses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Approval Pdf  colour xerox </t>
+  </si>
+  <si>
+    <t>Multi Meter For Office Purpose  (flipkart)</t>
+  </si>
+  <si>
+    <t>Delivery charges from Vizag to Sompeta for  gas cutter set And hose pipe 100 meter</t>
+  </si>
+  <si>
+    <t>Crusher Wifi Reacharge Bill</t>
+  </si>
+  <si>
+    <t>Received Money From Rajashekhar Through Ph pay</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\₹#,##0.00"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -289,7 +433,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -491,11 +635,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -625,6 +782,36 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -634,6 +821,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,22 +1155,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -1315,22 +1509,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -1961,13 +2155,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B13B25-A20B-4D4C-9830-1B03E23D3D53}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="49.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
@@ -1975,22 +2169,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
@@ -2273,6 +2467,11 @@
         <v>4100</v>
       </c>
     </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:G3" xr:uid="{80B13B25-A20B-4D4C-9830-1B03E23D3D53}"/>
   <mergeCells count="2">
@@ -2282,4 +2481,698 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95ADD498-C75C-4822-983F-D8C04F0CD194}">
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="58.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="54">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="54"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="52">
+        <v>204</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39">
+        <v>10000</v>
+      </c>
+      <c r="G6" s="39">
+        <f>G4-E6+F6</f>
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="52">
+        <v>205</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="17">
+        <v>58</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="39">
+        <v>650</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39">
+        <f>G6-E7+F7</f>
+        <v>13450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="52">
+        <v>206</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="39">
+        <v>13546</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39">
+        <f>G7-E8+F8</f>
+        <v>-96</v>
+      </c>
+      <c r="K8" s="68"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="52">
+        <v>207</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39">
+        <v>8500</v>
+      </c>
+      <c r="G9" s="39">
+        <f>G8-E9+F9</f>
+        <v>8404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="52">
+        <v>208</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="39">
+        <v>100</v>
+      </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39">
+        <f t="shared" ref="G10:G19" si="0">G9-E10+F10</f>
+        <v>8304</v>
+      </c>
+      <c r="K10" s="68"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="52">
+        <v>209</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="39">
+        <v>60</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39">
+        <f t="shared" si="0"/>
+        <v>8244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="52">
+        <v>210</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="60">
+        <v>97</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="39">
+        <v>320</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39">
+        <f t="shared" si="0"/>
+        <v>7924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="52">
+        <v>211</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="39">
+        <v>100</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39">
+        <f t="shared" si="0"/>
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="52">
+        <v>212</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="39">
+        <v>330</v>
+      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39">
+        <f t="shared" si="0"/>
+        <v>7494</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="52">
+        <v>213</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="39">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39">
+        <f t="shared" si="0"/>
+        <v>6494</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="52">
+        <v>214</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="39">
+        <v>14721</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39">
+        <f t="shared" si="0"/>
+        <v>-8227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="52">
+        <v>215</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39">
+        <v>15000</v>
+      </c>
+      <c r="G17" s="39">
+        <f t="shared" si="0"/>
+        <v>6773</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="52">
+        <v>216</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="42">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39">
+        <f t="shared" si="0"/>
+        <v>5773</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="39">
+        <v>217</v>
+      </c>
+      <c r="B19" s="40">
+        <v>46032</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="39">
+        <v>1391</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39">
+        <f t="shared" si="0"/>
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="61">
+        <v>218</v>
+      </c>
+      <c r="B20" s="62">
+        <v>46062</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="39">
+        <v>50</v>
+      </c>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39">
+        <f>G19-E20+F20</f>
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="61"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39">
+        <f t="shared" ref="G21:G22" si="1">G20-E21+F21</f>
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C22" s="39"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39">
+        <f t="shared" si="1"/>
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="44">
+        <f>SUM(E6:E20)</f>
+        <v>33268</v>
+      </c>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44">
+        <f>G21-E21+F21</f>
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="41"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="67"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="29">
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="52">
+        <v>219</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="53">
+        <v>200</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="51">
+        <f>G30-E31+F31</f>
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="52">
+        <v>220</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="53">
+        <v>160</v>
+      </c>
+      <c r="F32" s="32"/>
+      <c r="G32" s="51">
+        <f t="shared" ref="G32:G38" si="2">G31-E32+F32</f>
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="52">
+        <v>221</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="53">
+        <v>200</v>
+      </c>
+      <c r="F33" s="32"/>
+      <c r="G33" s="51">
+        <f t="shared" si="2"/>
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="52">
+        <v>222</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="53">
+        <v>100</v>
+      </c>
+      <c r="F34" s="32"/>
+      <c r="G34" s="51">
+        <f t="shared" si="2"/>
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="52">
+        <v>223</v>
+      </c>
+      <c r="B35" s="59">
+        <v>46062</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="53">
+        <v>30</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="51">
+        <f t="shared" si="2"/>
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="52">
+        <v>224</v>
+      </c>
+      <c r="B36" s="59">
+        <v>46062</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="53">
+        <v>771</v>
+      </c>
+      <c r="F36" s="32"/>
+      <c r="G36" s="51">
+        <f t="shared" si="2"/>
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="52">
+        <v>225</v>
+      </c>
+      <c r="B37" s="59">
+        <v>46062</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="53"/>
+      <c r="F37" s="32">
+        <v>1000</v>
+      </c>
+      <c r="G37" s="51">
+        <f t="shared" si="2"/>
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="52"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="51">
+        <f t="shared" si="2"/>
+        <v>3871</v>
+      </c>
+      <c r="I38" s="68"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="52"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="46">
+        <f>SUM(E31:E37)</f>
+        <v>1461</v>
+      </c>
+      <c r="F39" s="46"/>
+      <c r="G39" s="45">
+        <f>G38-E38+F38</f>
+        <v>3871</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G18" xr:uid="{95ADD498-C75C-4822-983F-D8C04F0CD194}"/>
+  <mergeCells count="4">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="E28:G28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>